--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487614_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487614_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.231</v>
+        <v>4.176</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3596</v>
+        <v>7.0593</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.1286</v>
+        <v>-2.8833</v>
       </c>
       <c r="G2" t="n">
         <v>6.6168</v>
@@ -610,13 +610,13 @@
         <v>1.3582</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2858</v>
+        <v>0.2308</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4867</v>
+        <v>0.1864</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.201</v>
+        <v>0.0443</v>
       </c>
       <c r="V2" t="n">
         <v>-3.0597</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9645</v>
+        <v>2.3194</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5444</v>
+        <v>1.8447</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4201</v>
+        <v>0.4746</v>
       </c>
       <c r="G3" t="n">
         <v>1.2713</v>
@@ -688,13 +688,13 @@
         <v>0.3881</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2306</v>
+        <v>0.1242</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3028</v>
+        <v>-0.0025</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0722</v>
+        <v>0.1267</v>
       </c>
       <c r="V3" t="n">
         <v>1.506</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. DIAZ ZARZUELA</t>
+          <t>L. VALERA VILLEGAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5292</v>
+        <v>0.4729</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8965</v>
+        <v>-0.1327</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3673</v>
+        <v>0.6056</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1502</v>
+        <v>0.379</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.3523</v>
+        <v>-2.1791</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2021</v>
+        <v>2.5581</v>
       </c>
       <c r="J4" t="n">
-        <v>0.731</v>
+        <v>0.8275</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.9484</v>
+        <v>-0.6797</v>
       </c>
       <c r="L4" t="n">
-        <v>2.6794</v>
+        <v>1.5071</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8812</v>
+        <v>-0.4485</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4039</v>
+        <v>-1.4995</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5227000000000001</v>
+        <v>1.051</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.1642</v>
+        <v>0.194</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7761</v>
+        <v>2.1344</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1839</v>
+        <v>-0.1001</v>
       </c>
       <c r="T4" t="n">
-        <v>1.882</v>
+        <v>-0.2437</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3019</v>
+        <v>0.1436</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6597</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>1.2239</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5642</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. DIALLO</t>
+          <t>F. DIAZ ZARZUELA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2542</v>
+        <v>0.219</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2906</v>
+        <v>0.6953</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0365</v>
+        <v>-0.4763</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.8687</v>
+        <v>-0.1502</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.3195</v>
+        <v>-3.3523</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4509</v>
+        <v>3.2021</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.3525</v>
+        <v>0.731</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.2862</v>
+        <v>-1.9484</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9337</v>
+        <v>2.6794</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5162</v>
+        <v>-0.8812</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.0333</v>
+        <v>-1.4039</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5172</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="P5" t="n">
         <v>-1.1642</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9105</v>
+        <v>-1.9403</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7463</v>
+        <v>0.7761</v>
       </c>
       <c r="S5" t="n">
-        <v>3.6855</v>
+        <v>0.8737</v>
       </c>
       <c r="T5" t="n">
-        <v>1.882</v>
+        <v>0.6808</v>
       </c>
       <c r="U5" t="n">
-        <v>1.8035</v>
+        <v>0.1929</v>
       </c>
       <c r="V5" t="n">
-        <v>1.6015</v>
+        <v>0.6597</v>
       </c>
       <c r="W5" t="n">
-        <v>3.6716</v>
+        <v>1.2239</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.0701</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. VALERA VILLEGAS</t>
+          <t>M. DIALLO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1726</v>
+        <v>-0.837</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.433</v>
+        <v>0.2896</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6056</v>
+        <v>-1.1266</v>
       </c>
       <c r="G6" t="n">
-        <v>0.379</v>
+        <v>-2.8687</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.1791</v>
+        <v>-4.3195</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5581</v>
+        <v>1.4509</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8275</v>
+        <v>-1.3525</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6797</v>
+        <v>-2.2862</v>
       </c>
       <c r="L6" t="n">
-        <v>1.5071</v>
+        <v>0.9337</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4485</v>
+        <v>-1.5162</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4995</v>
+        <v>-2.0333</v>
       </c>
       <c r="O6" t="n">
-        <v>1.051</v>
+        <v>0.5172</v>
       </c>
       <c r="P6" t="n">
-        <v>0.194</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9403</v>
+        <v>-2.9105</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1344</v>
+        <v>1.7463</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4004</v>
+        <v>1.5943</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.544</v>
+        <v>0.881</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1436</v>
+        <v>0.7134</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.6015</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2239</v>
+        <v>3.6716</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2239</v>
+        <v>-2.0701</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9145</v>
+        <v>-0.8872</v>
       </c>
       <c r="E7" t="n">
         <v>-0.2423</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6722</v>
+        <v>-0.645</v>
       </c>
       <c r="G7" t="n">
         <v>-0.6904</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2241</v>
+        <v>-0.1968</v>
       </c>
       <c r="T7" t="n">
         <v>-0.2423</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9718</v>
+        <v>-1.226</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0924</v>
+        <v>-0.5919</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8794</v>
+        <v>-0.6341</v>
       </c>
       <c r="G8" t="n">
         <v>0.6468</v>
@@ -1078,13 +1078,13 @@
         <v>0.7761</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8425</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6057</v>
+        <v>-0.1052</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2369</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6119</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1121</v>
+        <v>-1.6022</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.6809</v>
+        <v>-2.5798</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5688</v>
+        <v>0.9776</v>
       </c>
       <c r="G9" t="n">
         <v>-0.4363</v>
@@ -1156,13 +1156,13 @@
         <v>2.1344</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.522</v>
+        <v>-0.0121</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7268</v>
+        <v>0.3743</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7952</v>
+        <v>-0.3864</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3776</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2051</v>
+        <v>-2.5684</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0597</v>
+        <v>-2.5592</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1454</v>
+        <v>-0.0091</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4413</v>
@@ -1234,13 +1234,13 @@
         <v>1.9403</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7458</v>
+        <v>-0.1091</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.544</v>
+        <v>-0.0435</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2019</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>-0.0478</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3909</v>
+        <v>-3.5094</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.6068</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.1979</v>
+        <v>-4.1162</v>
       </c>
       <c r="G11" t="n">
         <v>-1.8108</v>
@@ -1312,13 +1312,13 @@
         <v>0.3881</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4796</v>
+        <v>0.3611</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4251</v>
+        <v>0.2249</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0545</v>
+        <v>0.1363</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4477</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4429</v>
+        <v>-3.442899999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>4.389800000000001</v>
+        <v>4.3898</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.832799999999999</v>
+        <v>-7.832800000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>1.516199999999999</v>
+        <v>1.5162</v>
       </c>
       <c r="H12" t="n">
         <v>-18.7266</v>
@@ -1366,7 +1366,7 @@
         <v>8.630800000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>-6.384800000000001</v>
+        <v>-6.384799999999999</v>
       </c>
       <c r="L12" t="n">
         <v>15.0155</v>
@@ -1378,7 +1378,7 @@
         <v>-12.3418</v>
       </c>
       <c r="O12" t="n">
-        <v>5.227300000000001</v>
+        <v>5.2273</v>
       </c>
       <c r="P12" t="n">
         <v>-4.8508</v>
@@ -1390,13 +1390,13 @@
         <v>11.642</v>
       </c>
       <c r="S12" t="n">
-        <v>2.669400000000001</v>
+        <v>2.6693</v>
       </c>
       <c r="T12" t="n">
-        <v>1.710199999999999</v>
+        <v>1.7102</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9588999999999999</v>
+        <v>0.9590000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-2.7775</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.5048</v>
+        <v>7.5232</v>
       </c>
       <c r="E13" t="n">
-        <v>6.4407</v>
+        <v>6.5408</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0641</v>
+        <v>0.9823</v>
       </c>
       <c r="G13" t="n">
         <v>2.1395</v>
@@ -1468,13 +1468,13 @@
         <v>1.7463</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5884</v>
+        <v>-0.57</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2412</v>
+        <v>-0.1411</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3472</v>
+        <v>-0.429</v>
       </c>
       <c r="V13" t="n">
         <v>5.1776</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. GOMA</t>
+          <t>T. VERDERA BENASSAR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.109</v>
+        <v>3.0387</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0619</v>
+        <v>3.1953</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9529</v>
+        <v>-0.1566</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3462</v>
+        <v>-1.003</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4451</v>
+        <v>2.9181</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.7913</v>
+        <v>-3.9212</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2011</v>
+        <v>-0.9409999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>1.0793</v>
+        <v>1.6066</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1218</v>
+        <v>-2.5475</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5473</v>
+        <v>-0.0621</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3658</v>
+        <v>1.3116</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.9131</v>
+        <v>-1.3737</v>
       </c>
       <c r="P14" t="n">
-        <v>1.9403</v>
+        <v>2.9105</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>2.9105</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8925</v>
+        <v>-0.4702</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7608</v>
+        <v>-0.1472</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1317</v>
+        <v>-0.323</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3776</v>
+        <v>1.6015</v>
       </c>
       <c r="W14" t="n">
-        <v>2.0701</v>
+        <v>4.2836</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.4477</v>
+        <v>-2.6821</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3656</v>
+        <v>2.1921</v>
       </c>
       <c r="E15" t="n">
-        <v>1.925</v>
+        <v>1.4245</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4406</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>2.0859</v>
@@ -1624,13 +1624,13 @@
         <v>2.1344</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0857</v>
+        <v>-0.0878</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3656</v>
+        <v>-0.1349</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2799</v>
+        <v>0.0471</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. VERDERA BENASSAR</t>
+          <t>G. GOMA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1745</v>
+        <v>1.5897</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4946</v>
+        <v>2.7606</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3202</v>
+        <v>-1.1709</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.003</v>
+        <v>-0.3462</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9181</v>
+        <v>1.4451</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.9212</v>
+        <v>-1.7913</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.9409999999999999</v>
+        <v>1.2011</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6066</v>
+        <v>1.0793</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.5475</v>
+        <v>0.1218</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0621</v>
+        <v>-1.5473</v>
       </c>
       <c r="N16" t="n">
-        <v>1.3116</v>
+        <v>0.3658</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.3737</v>
+        <v>-1.9131</v>
       </c>
       <c r="P16" t="n">
-        <v>2.9105</v>
+        <v>1.9403</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R16" t="n">
         <v>2.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3344</v>
+        <v>0.3732</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8479</v>
+        <v>0.4595</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4865</v>
+        <v>-0.0863</v>
       </c>
       <c r="V16" t="n">
-        <v>1.6015</v>
+        <v>-0.3776</v>
       </c>
       <c r="W16" t="n">
-        <v>4.2836</v>
+        <v>2.0701</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.6821</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6132</v>
+        <v>0.7406</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5998</v>
+        <v>0.6999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0135</v>
+        <v>0.0407</v>
       </c>
       <c r="G17" t="n">
         <v>1.6496</v>
@@ -1780,13 +1780,13 @@
         <v>0.3881</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2005</v>
+        <v>-0.0732</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1211</v>
+        <v>-0.021</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0794</v>
+        <v>-0.0521</v>
       </c>
       <c r="V17" t="n">
         <v>-1.2239</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4732</v>
+        <v>0.3463</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7049</v>
+        <v>0.9051</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2317</v>
+        <v>-0.5588</v>
       </c>
       <c r="G18" t="n">
         <v>1.0051</v>
@@ -1858,13 +1858,13 @@
         <v>0.5821</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4737</v>
+        <v>-0.6006</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6662</v>
+        <v>-0.466</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1925</v>
+        <v>-0.1346</v>
       </c>
       <c r="V18" t="n">
         <v>0.3299</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. MORENO GUTIERREZ</t>
+          <t>D. SHIELDS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0822</v>
+        <v>0.2368</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2738</v>
+        <v>0.8988</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1916</v>
+        <v>-0.662</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2449</v>
+        <v>0.4855</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2943</v>
+        <v>0.3987</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0494</v>
+        <v>0.0868</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4237</v>
+        <v>1.9321</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3831</v>
+        <v>0.0824</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0406</v>
+        <v>1.8497</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1788</v>
+        <v>-1.4466</v>
       </c>
       <c r="N19" t="n">
-        <v>0.9112</v>
+        <v>0.3164</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.09</v>
+        <v>-1.7629</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3881</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3881</v>
+        <v>0.9702</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6732</v>
+        <v>-0.2487</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8501</v>
+        <v>-0.0631</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.177</v>
+        <v>-0.1856</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0741</v>
+        <v>0.1742</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0295</v>
+        <v>-0.9294</v>
       </c>
       <c r="F20" t="n">
         <v>1.1037</v>
@@ -2014,10 +2014,10 @@
         <v>0.9702</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2187</v>
+        <v>-0.1186</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1211</v>
+        <v>-0.021</v>
       </c>
       <c r="U20" t="n">
         <v>-0.09760000000000001</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. SHIELDS</t>
+          <t>F. MORENO GUTIERREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.6913</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5985</v>
+        <v>0.473</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6893</v>
+        <v>-1.1643</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4855</v>
+        <v>0.2449</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3987</v>
+        <v>1.2943</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0868</v>
+        <v>-1.0494</v>
       </c>
       <c r="J21" t="n">
-        <v>1.9321</v>
+        <v>0.4237</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0824</v>
+        <v>0.3831</v>
       </c>
       <c r="L21" t="n">
-        <v>1.8497</v>
+        <v>0.0406</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4466</v>
+        <v>-0.1788</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3164</v>
+        <v>0.9112</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.7629</v>
+        <v>-1.09</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.3881</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9702</v>
+        <v>0.3881</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5763</v>
+        <v>-0.1004</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3634</v>
+        <v>0.0493</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2129</v>
+        <v>-0.1497</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="22">
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7736</v>
+        <v>-1.4733</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7295</v>
+        <v>-0.4292</v>
       </c>
       <c r="F22" t="n">
         <v>-1.0441</v>
@@ -2170,10 +2170,10 @@
         <v>0.5821</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2669</v>
+        <v>0.0334</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3028</v>
+        <v>-0.0025</v>
       </c>
       <c r="U22" t="n">
         <v>0.0359</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6313</v>
+        <v>-2.722</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9661</v>
+        <v>-1.866</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6652</v>
+        <v>-0.856</v>
       </c>
       <c r="G23" t="n">
         <v>-0.0667</v>
@@ -2248,13 +2248,13 @@
         <v>0.9702</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3706</v>
+        <v>-0.4612</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1817</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1889</v>
+        <v>-0.3796</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2239</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.4581</v>
+        <v>-7.5121</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.5414</v>
+        <v>-5.8407</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.9167</v>
+        <v>-1.6714</v>
       </c>
       <c r="G24" t="n">
         <v>-6.2251</v>
@@ -2326,13 +2326,13 @@
         <v>1.9403</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2912</v>
+        <v>-0.3452</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0902</v>
+        <v>-0.3895</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.201</v>
+        <v>0.0443</v>
       </c>
       <c r="V24" t="n">
         <v>-0.9418</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>3.442800000000002</v>
+        <v>3.442899999999998</v>
       </c>
       <c r="E25" t="n">
-        <v>7.832699999999998</v>
+        <v>7.832700000000003</v>
       </c>
       <c r="F25" t="n">
         <v>-4.3898</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.516100000000001</v>
+        <v>-1.5161</v>
       </c>
       <c r="H25" t="n">
         <v>18.7265</v>
@@ -2383,7 +2383,7 @@
         <v>12.3417</v>
       </c>
       <c r="L25" t="n">
-        <v>-5.227300000000001</v>
+        <v>-5.2273</v>
       </c>
       <c r="M25" t="n">
         <v>-8.630700000000001</v>
@@ -2407,10 +2407,10 @@
         <v>-2.6693</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9591000000000002</v>
+        <v>-0.9591000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.7103</v>
+        <v>-1.7102</v>
       </c>
       <c r="V25" t="n">
         <v>2.7776</v>
